--- a/src/assets/月結匯出.xlsx
+++ b/src/assets/月結匯出.xlsx
@@ -26,35 +26,107 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>客戶代號</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帳單組</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>筆數</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>產品</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用油</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>銷售金額</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>統編</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>抬頭</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>客戶代號</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>帳單組</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>筆數</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>產品</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>用油</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>銷售金額</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>統編</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>抬頭</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -65,7 +137,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -80,6 +152,24 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Ti"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Ti"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -104,23 +194,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -404,19 +497,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="11.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="44.625" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.25" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="16.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.125" style="6" customWidth="1"/>
     <col min="7" max="7" width="19.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="34.75" customWidth="1"/>
+    <col min="8" max="8" width="34.75" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -429,7 +523,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">

--- a/src/assets/月結匯出.xlsx
+++ b/src/assets/月結匯出.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <r>
       <rPr>
@@ -127,6 +127,10 @@
       </rPr>
       <t>抬頭</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>客戶名稱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -194,7 +198,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -215,6 +219,9 @@
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -496,43 +503,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="11.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="44.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="16.125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="19.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="34.75" style="4" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="4"/>
+    <col min="2" max="2" width="32.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="44.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="16.125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="19.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="34.75" style="4" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16.5">
+    <row r="1" spans="1:9" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
